--- a/artfynd/A 59780-2021 artfynd.xlsx
+++ b/artfynd/A 59780-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59780-2021 artfynd.xlsx
+++ b/artfynd/A 59780-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,327 +1024,6 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>112605122</v>
-      </c>
-      <c r="B5" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ruskträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>678876</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7198127</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>112605123</v>
-      </c>
-      <c r="B6" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Ruskträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>678828</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7198123</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112605124</v>
-      </c>
-      <c r="B7" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ruskträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>678848</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7198105</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59780-2021 artfynd.xlsx
+++ b/artfynd/A 59780-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109910437</v>
+        <v>112605122</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>678876.3841499923</v>
+        <v>678877</v>
       </c>
       <c r="R2" t="n">
-        <v>7198127.229237829</v>
+        <v>7198127</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-11-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109910438</v>
+        <v>112605123</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678827.5312229252</v>
+        <v>678828</v>
       </c>
       <c r="R3" t="n">
-        <v>7198123.458970684</v>
+        <v>7198124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2022-11-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109910439</v>
+        <v>112605124</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678847.8596821402</v>
+        <v>678848</v>
       </c>
       <c r="R4" t="n">
-        <v>7198104.639295656</v>
+        <v>7198105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2022-11-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 59780-2021 artfynd.xlsx
+++ b/artfynd/A 59780-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605122</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605123</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605124</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>